--- a/logs/tasks-list/tasks-list-news-scape.xlsx
+++ b/logs/tasks-list/tasks-list-news-scape.xlsx
@@ -2385,9 +2385,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010088BB270C8F5FC24BA49AFFE556196667" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="caed7ae97c664de60029983d3ac4638e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c36903d5-5ed0-4454-a196-b1a2f9ebaa03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e1819aac575aee29cb2a2f708b09de1" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010088BB270C8F5FC24BA49AFFE556196667" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bebf88d6575d16559b5f30f0a2a701c1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c36903d5-5ed0-4454-a196-b1a2f9ebaa03" xmlns:ns3="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7261e384d67fa0b6a688911c7473044a" ns2:_="" ns3:_="">
     <xsd:import namespace="c36903d5-5ed0-4454-a196-b1a2f9ebaa03"/>
+    <xsd:import namespace="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -2397,6 +2398,11 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2421,6 +2427,43 @@
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8f7c344f-19d0-4f45-b23a-2df2b546d212" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{4dc7bc77-2376-40bf-86a0-4a9e9b5c2537}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -2533,26 +2576,17 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <TaxCatchAll xmlns="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c36903d5-5ed0-4454-a196-b1a2f9ebaa03">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2DCB1F6-65D9-41E2-8F81-B6B7E3279A7D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c36903d5-5ed0-4454-a196-b1a2f9ebaa03"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{255787F6-6FAC-4995-81ED-B301959341D9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/logs/tasks-list/tasks-list-news-scape.xlsx
+++ b/logs/tasks-list/tasks-list-news-scape.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="89">
   <si>
     <t>Module</t>
   </si>
@@ -187,6 +187,9 @@
     <t>Danh sách entity phục vụ nhận diện cổ phiếu, doanh nghiệp, ngành</t>
   </si>
   <si>
+    <t>Kiểm tra chức năng nhận diện entity</t>
+  </si>
+  <si>
     <t>Verify entity recognition accuracy trên sample articles</t>
   </si>
   <si>
@@ -291,12 +294,6 @@
   </si>
   <si>
     <t>Đọc và trích xuất nội dung từ database và url</t>
-  </si>
-  <si>
-    <t>tóm tắt</t>
-  </si>
-  <si>
-    <t>tóm tát nội dung entity</t>
   </si>
 </sst>
 </file>
@@ -364,7 +361,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -387,23 +384,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -443,9 +429,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1337,7 +1320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1355,7 +1338,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>0</v>
@@ -1408,7 +1391,7 @@
         <v>14</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
@@ -1441,7 +1424,7 @@
         <v>14</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>15</v>
@@ -1501,7 +1484,7 @@
         <v>24</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>15</v>
@@ -1536,7 +1519,7 @@
         <v>24</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>15</v>
@@ -1571,7 +1554,7 @@
         <v>33</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>15</v>
@@ -1583,7 +1566,7 @@
         <v>34</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -1606,7 +1589,7 @@
         <v>33</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>15</v>
@@ -1618,7 +1601,7 @@
         <v>36</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1641,10 +1624,10 @@
         <v>33</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="8" t="s">
@@ -1672,7 +1655,7 @@
         <v>33</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>15</v>
@@ -1684,7 +1667,7 @@
         <v>40</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -1695,7 +1678,7 @@
         <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>31</v>
@@ -1707,7 +1690,7 @@
         <v>24</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>15</v>
@@ -1727,29 +1710,29 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K12" s="3"/>
     </row>
@@ -1758,10 +1741,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>51</v>
@@ -1773,14 +1756,14 @@
         <v>24</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K13" s="3"/>
     </row>
@@ -1789,10 +1772,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>51</v>
@@ -1804,14 +1787,14 @@
         <v>14</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K14" s="3"/>
     </row>
@@ -1820,10 +1803,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>51</v>
@@ -1835,14 +1818,14 @@
         <v>24</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K15" s="3"/>
     </row>
@@ -1851,10 +1834,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>51</v>
@@ -1866,14 +1849,14 @@
         <v>24</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K16" s="3"/>
     </row>
@@ -1882,10 +1865,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>51</v>
@@ -1897,14 +1880,14 @@
         <v>24</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K17" s="3"/>
     </row>
@@ -1919,7 +1902,7 @@
         <v>43</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>23</v>
@@ -1928,7 +1911,7 @@
         <v>24</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
@@ -1940,7 +1923,7 @@
         <v>44</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -1954,7 +1937,7 @@
         <v>45</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>23</v>
@@ -1963,7 +1946,7 @@
         <v>24</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
@@ -1989,7 +1972,7 @@
         <v>47</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>23</v>
@@ -1998,7 +1981,7 @@
         <v>24</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>48</v>
@@ -2010,7 +1993,7 @@
         <v>49</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -2024,7 +2007,7 @@
         <v>50</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>32</v>
@@ -2033,7 +2016,7 @@
         <v>33</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>20</v>
@@ -2052,10 +2035,10 @@
         <v>41</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>23</v>
@@ -2064,21 +2047,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C23" s="15" t="s">
-        <v>89</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K28"/>
@@ -2099,7 +2077,7 @@
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20:K20 A2:K19 A20:F20 A21:K22 C23">
+  <conditionalFormatting sqref="H20:K20 A2:K19 A20:F20 A21:K22">
     <cfRule type="cellIs" dxfId="48" priority="20" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
@@ -2193,16 +2171,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -2210,10 +2188,10 @@
         <v>12</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>15</v>
@@ -2225,10 +2203,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>15</v>
@@ -2239,25 +2217,25 @@
         <v>51</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2566,15 +2544,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" xsi:nil="true"/>
@@ -2585,30 +2554,32 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{255787F6-6FAC-4995-81ED-B301959341D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9160F235-8519-47FB-960A-18F79E561E23}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C3A554-6B80-41C4-A4F6-F247CBBD1B04}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2C74649-0119-4C04-A90A-3FD8A7565BA3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C3A554-6B80-41C4-A4F6-F247CBBD1B04}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c36903d5-5ed0-4454-a196-b1a2f9ebaa03"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>